--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484789_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484789_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.6245</v>
+        <v>11.7652</v>
       </c>
       <c r="E2" t="n">
-        <v>9.7203</v>
+        <v>9.6229</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9042</v>
+        <v>2.1423</v>
       </c>
       <c r="G2" t="n">
         <v>8.483000000000001</v>
@@ -610,13 +610,13 @@
         <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8206</v>
+        <v>0.9613</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3803</v>
+        <v>0.2829</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4403</v>
+        <v>0.6784</v>
       </c>
       <c r="V2" t="n">
         <v>0.6226</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>U. ZAMORA MANA</t>
+          <t>S. SIDDIQUE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6991</v>
+        <v>6.9155</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3451</v>
+        <v>3.919</v>
       </c>
       <c r="F3" t="n">
-        <v>4.354</v>
+        <v>2.9965</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8502</v>
+        <v>3.3934</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2136</v>
+        <v>2.7328</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6365</v>
+        <v>0.6606</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1277</v>
+        <v>3.4597</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9461000000000001</v>
+        <v>3.254</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1816</v>
+        <v>0.2057</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2775</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7325</v>
+        <v>-0.5212</v>
       </c>
       <c r="O3" t="n">
         <v>0.455</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7548</v>
+        <v>2.2644</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0757</v>
+        <v>-0.1887</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8305</v>
+        <v>2.4531</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5471</v>
+        <v>0.9558</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4443</v>
+        <v>0.3462</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1029</v>
+        <v>0.6097</v>
       </c>
       <c r="V3" t="n">
-        <v>1.547</v>
+        <v>0.3018</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8488</v>
+        <v>0.3018</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. SIDDIQUE</t>
+          <t>J. ORTOLA TOMAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9967</v>
+        <v>5.3137</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5292</v>
+        <v>2.4142</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4674</v>
+        <v>2.8995</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3934</v>
+        <v>3.0794</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7328</v>
+        <v>3.1617</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6606</v>
+        <v>-0.0823</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4597</v>
+        <v>2.2304</v>
       </c>
       <c r="K4" t="n">
-        <v>3.254</v>
+        <v>2.7892</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2057</v>
+        <v>-0.5588</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0.8491</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5212</v>
+        <v>0.3725</v>
       </c>
       <c r="O4" t="n">
-        <v>0.455</v>
+        <v>0.4765</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2644</v>
+        <v>0.7548</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4531</v>
+        <v>1.6983</v>
       </c>
       <c r="S4" t="n">
-        <v>0.037</v>
+        <v>1.4795</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0436</v>
+        <v>1.1273</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0806</v>
+        <v>0.3522</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ORTOLA TOMAS</t>
+          <t>U. ZAMORA MANA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8441</v>
+        <v>4.8782</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7065</v>
+        <v>1.3707</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1376</v>
+        <v>3.5075</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0794</v>
+        <v>0.8502</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1617</v>
+        <v>0.2136</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0823</v>
+        <v>0.6365</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2304</v>
+        <v>1.1277</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7892</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5588</v>
+        <v>0.1816</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8491</v>
+        <v>-0.2775</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3725</v>
+        <v>-0.7325</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4765</v>
+        <v>0.455</v>
       </c>
       <c r="P5" t="n">
         <v>0.7548</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9435</v>
+        <v>-2.0757</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6983</v>
+        <v>2.8305</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0099</v>
+        <v>1.7262</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4196</v>
+        <v>0.4699</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5903</v>
+        <v>1.2563</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.8488</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6641</v>
+        <v>3.0622</v>
       </c>
       <c r="E6" t="n">
-        <v>1.084</v>
+        <v>1.3763</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5801</v>
+        <v>1.6859</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0018</v>
@@ -922,13 +922,13 @@
         <v>2.0757</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.9883</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1328</v>
+        <v>0.4251</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4574</v>
+        <v>0.5632</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. JIMENA LLORCA</t>
+          <t>R. AGBEKO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6315</v>
+        <v>2.2991</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4656</v>
+        <v>0.365</v>
       </c>
       <c r="F7" t="n">
-        <v>1.166</v>
+        <v>1.9341</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0498</v>
+        <v>5.5018</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6864</v>
+        <v>4.0382</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6365</v>
+        <v>1.4636</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1048</v>
+        <v>5.1126</v>
       </c>
       <c r="K7" t="n">
-        <v>0.655</v>
+        <v>3.7142</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5503</v>
+        <v>1.3984</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0549</v>
+        <v>0.3892</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0313</v>
+        <v>0.324</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0863</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.887</v>
+        <v>-3.9627</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1887</v>
+        <v>-5.661</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0757</v>
+        <v>1.6983</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9399</v>
+        <v>1.0618</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5495</v>
+        <v>0.9324</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3904</v>
+        <v>0.1294</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.019</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2452</v>
+        <v>-0.2828</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2278</v>
+        <v>2.1568</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1232</v>
+        <v>1.0257</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1046</v>
+        <v>1.1311</v>
       </c>
       <c r="G8" t="n">
         <v>0.8937</v>
@@ -1078,13 +1078,13 @@
         <v>0.5661</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4662</v>
+        <v>0.3952</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4144</v>
+        <v>0.317</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0517</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0.3018</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MARZIALI</t>
+          <t>S. JIMENA LLORCA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9587</v>
+        <v>2.0566</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.22</v>
+        <v>1.0758</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1787</v>
+        <v>0.9808</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1404</v>
+        <v>0.0498</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2161</v>
+        <v>0.6864</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0757</v>
+        <v>-0.6365</v>
       </c>
       <c r="J9" t="n">
-        <v>1.715</v>
+        <v>0.1048</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5746</v>
+        <v>0.655</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1404</v>
+        <v>-0.5503</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5746</v>
+        <v>-0.0549</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3584</v>
+        <v>0.0313</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2162</v>
+        <v>-0.0863</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3209</v>
+        <v>1.887</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0192</v>
+        <v>-0.1887</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6983</v>
+        <v>2.0757</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1392</v>
+        <v>1.365</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7824</v>
+        <v>1.1598</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3568</v>
+        <v>0.2052</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. AGBEKO</t>
+          <t>M. MARZIALI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5377</v>
+        <v>1.0747</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.317</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8547</v>
+        <v>1.7819</v>
       </c>
       <c r="G10" t="n">
-        <v>5.5018</v>
+        <v>1.1404</v>
       </c>
       <c r="H10" t="n">
-        <v>4.0382</v>
+        <v>1.2161</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4636</v>
+        <v>-0.0757</v>
       </c>
       <c r="J10" t="n">
-        <v>5.1126</v>
+        <v>1.715</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7142</v>
+        <v>1.5746</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3984</v>
+        <v>0.1404</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3892</v>
+        <v>-0.5746</v>
       </c>
       <c r="N10" t="n">
-        <v>0.324</v>
+        <v>-0.3584</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.2162</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.9627</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.661</v>
+        <v>-3.0192</v>
       </c>
       <c r="R10" t="n">
         <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3004</v>
+        <v>1.2552</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2504</v>
+        <v>0.2952</v>
       </c>
       <c r="U10" t="n">
-        <v>0.05</v>
+        <v>0.96</v>
       </c>
       <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="X10" t="n">
         <v>-0.3018</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.019</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.2828</v>
       </c>
     </row>
     <row r="11">
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. DAMULEVICIUS</t>
+          <t>M. JIMENA LLORCA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8125</v>
+        <v>0.8779</v>
       </c>
       <c r="E12" t="n">
-        <v>1.318</v>
+        <v>-0.4689</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5056</v>
+        <v>1.3468</v>
       </c>
       <c r="G12" t="n">
-        <v>2.0874</v>
+        <v>0.9008</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8123</v>
+        <v>-0.3592</v>
       </c>
       <c r="I12" t="n">
-        <v>1.275</v>
+        <v>1.26</v>
       </c>
       <c r="J12" t="n">
-        <v>1.682</v>
+        <v>0.1542</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0565</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.7403</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4054</v>
+        <v>0.7466</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2442</v>
+        <v>0.227</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6496</v>
+        <v>0.5196</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1322</v>
+        <v>0.7548</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0.7548</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1781</v>
+        <v>-0.1361</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2968</v>
+        <v>0.0185</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1187</v>
+        <v>-0.1546</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3208</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2262</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. JIMENA LLORCA</t>
+          <t>S. DAMULEVICIUS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5772</v>
+        <v>0.8292</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6637999999999999</v>
+        <v>1.1232</v>
       </c>
       <c r="F13" t="n">
-        <v>1.241</v>
+        <v>-0.2939</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9008</v>
+        <v>2.0874</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3592</v>
+        <v>0.8123</v>
       </c>
       <c r="I13" t="n">
-        <v>1.26</v>
+        <v>1.275</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1542</v>
+        <v>1.682</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5862000000000001</v>
+        <v>1.0565</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7403</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7466</v>
+        <v>0.4054</v>
       </c>
       <c r="N13" t="n">
-        <v>0.227</v>
+        <v>-0.2442</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5196</v>
+        <v>0.6496</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7548</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R13" t="n">
         <v>0.7548</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4368</v>
+        <v>0.1949</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1764</v>
+        <v>0.102</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2604</v>
+        <v>0.0929</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.3208</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.2262</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.0862</v>
+        <v>-0.7415</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.501</v>
+        <v>-2.5267</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4148</v>
+        <v>1.7851</v>
       </c>
       <c r="G14" t="n">
         <v>0.0489</v>
@@ -1546,13 +1546,13 @@
         <v>1.3209</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6254999999999999</v>
+        <v>0.7192</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2816</v>
+        <v>0.6927</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3439</v>
+        <v>0.0265</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>41.4386</v>
+        <v>41.43849999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>19.541</v>
+        <v>19.5409</v>
       </c>
       <c r="F15" t="n">
-        <v>21.8975</v>
+        <v>21.8976</v>
       </c>
       <c r="G15" t="n">
         <v>27.3779</v>
@@ -1594,7 +1594,7 @@
         <v>21.8578</v>
       </c>
       <c r="I15" t="n">
-        <v>5.519800000000001</v>
+        <v>5.519799999999999</v>
       </c>
       <c r="J15" t="n">
         <v>26.4126</v>
@@ -1603,10 +1603,10 @@
         <v>22.8439</v>
       </c>
       <c r="L15" t="n">
-        <v>3.5685</v>
+        <v>3.568499999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9656000000000002</v>
+        <v>0.9656</v>
       </c>
       <c r="N15" t="n">
         <v>-0.9859999999999998</v>
@@ -1615,7 +1615,7 @@
         <v>1.9512</v>
       </c>
       <c r="P15" t="n">
-        <v>2.830500000000002</v>
+        <v>2.8305</v>
       </c>
       <c r="Q15" t="n">
         <v>-16.983</v>
@@ -1627,7 +1627,7 @@
         <v>10.9663</v>
       </c>
       <c r="T15" t="n">
-        <v>6.1689</v>
+        <v>6.169000000000001</v>
       </c>
       <c r="U15" t="n">
         <v>4.797400000000001</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5924</v>
+        <v>0.1377</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4909</v>
+        <v>0.9063</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8985</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4299</v>
@@ -1702,13 +1702,13 @@
         <v>2.4531</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7889</v>
+        <v>-1.2436</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1118</v>
+        <v>-0.6964</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6771</v>
+        <v>-0.5472</v>
       </c>
       <c r="V16" t="n">
         <v>2.1886</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1854</v>
+        <v>-0.0805</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4943</v>
+        <v>0.202</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.309</v>
+        <v>-0.2825</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2931</v>
@@ -1780,13 +1780,13 @@
         <v>0.3774</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1011</v>
+        <v>-0.1648</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4732</v>
+        <v>0.1809</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3721</v>
+        <v>-0.3456</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. STANESCU</t>
+          <t>T. SODERMAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6983</v>
+        <v>-1.4074</v>
       </c>
       <c r="E18" t="n">
-        <v>0.404</v>
+        <v>-0.3587</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1023</v>
+        <v>-1.0487</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.5404</v>
+        <v>0.2803</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6981000000000001</v>
+        <v>0.3475</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8423</v>
+        <v>-0.0672</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2485</v>
+        <v>0.9902</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6591</v>
+        <v>1.0142</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9076</v>
+        <v>-0.0241</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2919</v>
+        <v>-0.7099</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.3572</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.0431</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1322</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1322</v>
+        <v>0.5661</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3892</v>
+        <v>-0.8198</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6525</v>
+        <v>-0.2166</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2633</v>
+        <v>-0.6031</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3208</v>
+        <v>-0.3018</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3208</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CONNELLY IV</t>
+          <t>R. STANESCU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6034</v>
+        <v>-1.4416</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6748</v>
+        <v>-0.1806</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2782</v>
+        <v>-1.261</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4856</v>
+        <v>-2.5404</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.4035</v>
+        <v>-0.6981000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9179</v>
+        <v>-1.8423</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4498</v>
+        <v>-0.2485</v>
       </c>
       <c r="K19" t="n">
-        <v>0.45</v>
+        <v>1.6591</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9998</v>
+        <v>-1.9076</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.9354</v>
+        <v>-2.2919</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.8535</v>
+        <v>-2.3572</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0819</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.1322</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8305</v>
+        <v>1.1322</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2874</v>
+        <v>-0.3542</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1141</v>
+        <v>0.0679</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1733</v>
+        <v>-0.422</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1696</v>
+        <v>0.3208</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1696</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. SODERMAN</t>
+          <t>J. CONNELLY IV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.838</v>
+        <v>-1.6694</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5536</v>
+        <v>0.7722</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2844</v>
+        <v>-2.4416</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2803</v>
+        <v>-2.4856</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3475</v>
+        <v>-3.4035</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0672</v>
+        <v>0.9179</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9902</v>
+        <v>2.4498</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0142</v>
+        <v>0.45</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0241</v>
+        <v>1.9998</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7099</v>
+        <v>-4.9354</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-3.8535</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0431</v>
+        <v>-1.0819</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1322</v>
+        <v>-2.8305</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5661</v>
+        <v>2.8305</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2504</v>
+        <v>-1.3534</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4115</v>
+        <v>-1.0166</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8388</v>
+        <v>-0.3367</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3018</v>
+        <v>2.1696</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.1696</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6018</v>
+        <v>-2.1977</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1699</v>
+        <v>-0.975</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.432</v>
+        <v>-1.2227</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9755</v>
@@ -2092,13 +2092,13 @@
         <v>0.5661</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0793</v>
+        <v>-0.6751</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3527</v>
+        <v>-0.1579</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7266</v>
+        <v>-0.5173</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9244</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7967</v>
+        <v>-2.3336</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2044</v>
+        <v>0.3018</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0011</v>
+        <v>-2.6354</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1041</v>
@@ -2170,13 +2170,13 @@
         <v>1.1322</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2968</v>
+        <v>-0.8337</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5879</v>
+        <v>-0.4904</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7089</v>
+        <v>-0.3433</v>
       </c>
       <c r="V22" t="n">
         <v>-1.528</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4046</v>
+        <v>-2.7948</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2913</v>
+        <v>0.001</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1133</v>
+        <v>-2.7958</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7433</v>
@@ -2248,13 +2248,13 @@
         <v>1.6983</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5672</v>
+        <v>-0.9575</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9994</v>
+        <v>-0.7071</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5678</v>
+        <v>-0.2504</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6036</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. VAL GUTIERREZ</t>
+          <t>J. MUNOZ PALENCIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.417</v>
+        <v>-9.281700000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.7578</v>
+        <v>-6.9856</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6592</v>
+        <v>-2.2961</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.6258</v>
+        <v>-5.6205</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.4309</v>
+        <v>-4.1634</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.1949</v>
+        <v>-1.4571</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.9878</v>
+        <v>-2.4133</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.8532</v>
+        <v>-1.1723</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.1346</v>
+        <v>-1.241</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.638</v>
+        <v>-3.2072</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5777</v>
+        <v>-2.9911</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0603</v>
+        <v>-0.2162</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.774</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.9062</v>
+        <v>-3.9627</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1322</v>
+        <v>2.2644</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6207</v>
+        <v>-1.3403</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4674</v>
+        <v>-0.6097</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1533</v>
+        <v>-0.7307</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6036</v>
+        <v>-0.6226</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. MUNOZ PALENCIA</t>
+          <t>S. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.8567</v>
+        <v>-9.4481</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.3754</v>
+        <v>-7.7578</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4813</v>
+        <v>-1.6903</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.6205</v>
+        <v>-5.6258</v>
       </c>
       <c r="H25" t="n">
-        <v>-4.1634</v>
+        <v>-3.4309</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.4571</v>
+        <v>-2.1949</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.4133</v>
+        <v>-2.9878</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.1723</v>
+        <v>-1.8532</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.241</v>
+        <v>-1.1346</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.2072</v>
+        <v>-2.638</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.9911</v>
+        <v>-1.5777</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2162</v>
+        <v>-1.0603</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.6983</v>
+        <v>-3.774</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.9627</v>
+        <v>-4.9062</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2644</v>
+        <v>1.1322</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.9152</v>
+        <v>-0.6519</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9994</v>
+        <v>-0.4674</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.1845</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.6226</v>
+        <v>0.6036</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.9999</v>
+        <v>-9.622199999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.0181</v>
+        <v>-7.8233</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.9818</v>
+        <v>-1.799</v>
       </c>
       <c r="G26" t="n">
         <v>-5.8397</v>
@@ -2482,13 +2482,13 @@
         <v>2.8305</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.6507</v>
+        <v>-1.273</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8789</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7718</v>
+        <v>-0.589</v>
       </c>
       <c r="V26" t="n">
         <v>-1.566</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-41.4386</v>
+        <v>-40.13930000000001</v>
       </c>
       <c r="E27" t="n">
         <v>-21.8977</v>
       </c>
       <c r="F27" t="n">
-        <v>-19.5411</v>
+        <v>-18.2417</v>
       </c>
       <c r="G27" t="n">
         <v>-27.3776</v>
@@ -2533,10 +2533,10 @@
         <v>-5.5198</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9651999999999985</v>
+        <v>-0.9651999999999998</v>
       </c>
       <c r="K27" t="n">
-        <v>0.9859999999999995</v>
+        <v>0.9860000000000007</v>
       </c>
       <c r="L27" t="n">
         <v>-1.9514</v>
@@ -2548,7 +2548,7 @@
         <v>-22.844</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.568700000000001</v>
+        <v>-3.5687</v>
       </c>
       <c r="P27" t="n">
         <v>-2.8305</v>
@@ -2560,16 +2560,16 @@
         <v>16.983</v>
       </c>
       <c r="S27" t="n">
-        <v>-10.9663</v>
+        <v>-9.667299999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.7974</v>
+        <v>-4.7973</v>
       </c>
       <c r="U27" t="n">
-        <v>-6.168799999999999</v>
+        <v>-4.8698</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.2637999999999998</v>
+        <v>-0.2638</v>
       </c>
       <c r="W27" t="n">
         <v>3.6786</v>
